--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:49:57+00:00</t>
+    <t>2026-08-28T07:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:24:31+00:00</t>
+    <t>2026-08-28T07:40:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:16:47+00:00</t>
+    <t>2026-08-28T12:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>T1b2</t>
+  </si>
+  <si>
+    <t>T1b3</t>
   </si>
   <si>
     <t>T1c</t>
@@ -498,7 +501,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -862,7 +865,15 @@
         <v>72</v>
       </c>
       <c r="B45" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
         <v>73</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:57:18+00:00</t>
+    <t>2026-08-28T14:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-tnm-t-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
